--- a/Documentacion/4 Zitrazo Planilla de Requerimientos.xlsx
+++ b/Documentacion/4 Zitrazo Planilla de Requerimientos.xlsx
@@ -1,227 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Datos\Proyecto Yuyito\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71A9652A-08E3-4386-8313-252182C584F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="4" r:id="rId1"/>
-    <sheet name="Requerimiento Inicial" sheetId="3" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requerimiento Inicial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
-  <si>
-    <t>[Nombre del Requerimiento]</t>
-  </si>
-  <si>
-    <t>Actores Relacionados</t>
-  </si>
-  <si>
-    <t>R.1</t>
-  </si>
-  <si>
-    <t>[R-N°]</t>
-  </si>
-  <si>
-    <t>R.2</t>
-  </si>
-  <si>
-    <t>R.3</t>
-  </si>
-  <si>
-    <t>R.4</t>
-  </si>
-  <si>
-    <t>R.5</t>
-  </si>
-  <si>
-    <t>R.6</t>
-  </si>
-  <si>
-    <t>R.7</t>
-  </si>
-  <si>
-    <t>R.8</t>
-  </si>
-  <si>
-    <t>R.9</t>
-  </si>
-  <si>
-    <t>R.10</t>
-  </si>
-  <si>
-    <t>R.11</t>
-  </si>
-  <si>
-    <t>R.12</t>
-  </si>
-  <si>
-    <t>R.13</t>
-  </si>
-  <si>
-    <t>R.14</t>
-  </si>
-  <si>
-    <t>R.15</t>
-  </si>
-  <si>
-    <t>Tipo Requerimiento
-[Funcional, No Funcional]</t>
-  </si>
-  <si>
-    <t>[Descripción corta del requerimiento]</t>
-  </si>
-  <si>
-    <t>Funcional</t>
-  </si>
-  <si>
-    <t>Todos los Actores que interactúen en el Sistema</t>
-  </si>
-  <si>
-    <t>Autentificar  Usuario al iniciar Sesión</t>
-  </si>
-  <si>
-    <t>Columna</t>
-  </si>
-  <si>
-    <t>Instrucciones</t>
-  </si>
-  <si>
-    <t>Código de identificación de mayor nivel definido para el requisito. Puede definirse con números, por ejemplo 001, 002, 003, y así sucesivamente.</t>
-  </si>
-  <si>
-    <t>Se proporciona una descripción de que comprende o en qué consiste el requisito. La descripción del requisito depende del tipo que sea, por ejemplo requisitos del negocio, requisitos de los interesados, requisitos funcionales, requisitos no funcionales, requisitos del proyecto o requisitos del producto (solución).</t>
-  </si>
-  <si>
-    <t>Puede ser solicitado, aprobado, asignado, completado, cancelado, diferido, aceptado, entre otros.</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado </t>
-  </si>
-  <si>
-    <t>Criterio de Aceptación</t>
-  </si>
-  <si>
-    <t>Lista los criterios de aceptación, una lista de puntos o condiciones específicas que deben cumplirse para poder registrar que el requisito ha sido satisfecho cuando se implemente en el Sistema.</t>
-  </si>
-  <si>
-    <t>El sistema debe autenticar la identidad de un Usuario que inicie sesión con su perfil para interactuar con el Sistema según su perfil. 
-Autenticará por Rut  y Clave Alfanumérica.</t>
-  </si>
-  <si>
-    <t>Se identifica el Tipo de Requerimiento como Funcional o no Funcional de aquellos que se asocian al desarrollo del Sistema.</t>
-  </si>
-  <si>
-    <t>Se identifica al Actor que como Usuario se relaciona al requerimiento definido.</t>
-  </si>
-  <si>
-    <t>Crear Cuentas de Usuario</t>
-  </si>
-  <si>
-    <t>Administrador Hostal</t>
-  </si>
-  <si>
-    <t>El Administrador podrá crear cuentas de usuaris para los Recepcionistas y para los Clientes Premium para que puedan trabajar en el sistema en base a sus atributos de usuario</t>
-  </si>
-  <si>
-    <t>Realiar una consulta de las Habitaciones disponibles por medio del sistema</t>
-  </si>
-  <si>
-    <t>Regisrar el ingreso y salida del pasajero en su ocupación de Habitación</t>
-  </si>
-  <si>
-    <t>Reservar habitación del Hostal. Por medio del sistema web disponible para el Cliente Vip</t>
-  </si>
-  <si>
-    <t>Que el sistema libere una habitación que se encuentre registrada como ocupada al cuando el recepcionista registre la salida del pasajero</t>
-  </si>
-  <si>
-    <t>Que el sistema calcule el monto de pago por concepto de uso de habitación al registrar la salida del pasajero</t>
-  </si>
-  <si>
-    <t>Recepcionista</t>
-  </si>
-  <si>
-    <t>Recepcionista o Administrador</t>
-  </si>
-  <si>
-    <t>Calcular el monto de pago de la habitación automáticamente</t>
-  </si>
-  <si>
-    <t>Liberar automáticamente la habitación al registrar la salida del pasajero</t>
-  </si>
-  <si>
-    <t>Registrar ocupación de la habitacion</t>
-  </si>
-  <si>
-    <t>Reservar Habitacion</t>
-  </si>
-  <si>
-    <t>Recepcionista o Cliente Vip</t>
-  </si>
-  <si>
-    <t>Verificar disponibilidad de habitaciones</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="0"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="0"/>
+      <sz val="16"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -240,13 +75,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,52 +140,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -616,478 +510,537 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="41.453125" customWidth="1"/>
-    <col min="2" max="2" width="146.453125" style="6" customWidth="1"/>
+    <col width="41.453125" customWidth="1" min="1" max="1"/>
+    <col width="146.453125" customWidth="1" style="6" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.5">
-      <c r="A1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="37" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="37" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="55.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Instrucciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>[Nombre del Requerimiento]</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Código de identificación de mayor nivel definido para el requisito. Puede definirse con números, por ejemplo 001, 002, 003, y así sucesivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="37" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Tipo Requerimiento
+[Funcional, No Funcional]</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Se identifica el Tipo de Requerimiento como Funcional o no Funcional de aquellos que se asocian al desarrollo del Sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.5" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Actores Relacionados</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Se identifica al Actor que como Usuario se relaciona al requerimiento definido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55.5" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>[Descripción corta del requerimiento]</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Se proporciona una descripción de que comprende o en qué consiste el requisito. La descripción del requisito depende del tipo que sea, por ejemplo requisitos del negocio, requisitos de los interesados, requisitos funcionales, requisitos no funcionales, requisitos del proyecto o requisitos del producto (solución).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Criterio de Aceptación</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Lista los criterios de aceptación, una lista de puntos o condiciones específicas que deben cumplirse para poder registrar que el requisito ha sido satisfecho cuando se implemente en el Sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36.75" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado </t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Puede ser solicitado, aprobado, asignado, completado, cancelado, diferido, aceptado, entre otros.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="1"/>
-    <col min="2" max="2" width="35.453125" customWidth="1"/>
-    <col min="3" max="3" width="25.6328125" customWidth="1"/>
-    <col min="4" max="4" width="25.453125" customWidth="1"/>
-    <col min="5" max="5" width="66.1796875" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col width="8.1796875" customWidth="1" min="1" max="1"/>
+    <col width="35.453125" customWidth="1" min="2" max="2"/>
+    <col width="25.6328125" customWidth="1" min="3" max="3"/>
+    <col width="25.453125" customWidth="1" min="4" max="4"/>
+    <col width="66.1796875" customWidth="1" min="5" max="5"/>
+    <col width="15.81640625" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    <row r="1" ht="40.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>R-N°</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Nombre del Requerimiento</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de Requerimiento</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Actores Relacionados</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Descripción del requerimiento</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.1</t>
+          <t>R.1</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar atraso con tarjeta SofoCard</t>
+          <t>Registrar atraso con tarjeta SofoCard</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector o Profesor</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al pasar la tarjeta del alumno por el lector, el sistema debe registrar el atraso indicando el alumno, la fecha y la hora.</t>
+          <t>Al pasar la tarjeta del alumno por el lector, el sistema debe registrar el atraso indicando el alumno, la fecha y la hora.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.2</t>
+          <t>R.2</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmar el registro en pantalla</t>
+          <t>Confirmar el registro en pantalla</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector, Profesor y Alumno</t>
+          <t>Inspector y Alumno</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Después de leer la tarjeta, la pantalla al costado del lector debe mostrar un mensaje confirmando que se registró el atraso del alumno correspondiente.</t>
+          <t>Después de leer la tarjeta, la pantalla al costado del lector debe mostrar un mensaje confirmando que se registró el atraso del alumno correspondiente.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.3</t>
+          <t>R.3</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detectar tarjeta no reconocida</t>
+          <t>Detectar tarjeta no reconocida</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector o Profesor</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si la tarjeta leída no corresponde a ningún alumno registrado, el sistema debe mostrar un mensaje de error en vez de registrar el atraso.</t>
+          <t>Si la tarjeta leída no corresponde a ningún alumno registrado, el sistema debe mostrar un mensaje de error en vez de registrar el atraso.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.4</t>
+          <t>R.4</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultar atrasos por alumno</t>
+          <t>Consultar atrasos por alumno</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema debe permitir buscar y ver todos los atrasos registrados de un alumno específico.</t>
+          <t>El sistema debe permitir buscar y ver todos los atrasos registrados de un alumno específico.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.5</t>
+          <t>R.5</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultar listado de atrasos del día</t>
+          <t>Consultar listado de atrasos del día</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema debe mostrar el listado completo de atrasos registrados durante el día.</t>
+          <t>El sistema debe mostrar el listado completo de atrasos registrados durante el día.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.6</t>
+          <t>R.6</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar alumno y su tarjeta SofoCard</t>
+          <t>Registrar alumno y su tarjeta SofoCard</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t>Administrador</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema debe permitir asociar una tarjeta nueva a un alumno con su nombre y curso.</t>
+          <t>El sistema debe permitir asociar una tarjeta nueva a un alumno con su nombre y curso.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.7</t>
+          <t>R.7</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dar de baja una tarjeta extraviada</t>
+          <t>Dar de baja una tarjeta extraviada</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcional</t>
+          <t>Funcional</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrador</t>
+          <t>Administrador</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si un alumno pierde su tarjeta, el sistema debe permitir invalidarla y asociar una nueva sin perder su historial de atrasos.</t>
+          <t>Si un alumno pierde su tarjeta, el sistema debe permitir invalidarla y asociar una nueva sin perder su historial de atrasos.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.8</t>
+          <t>R.8</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro rápido en la entrada</t>
+          <t>Registro rápido en la entrada</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Funcional</t>
+          <t>No Funcional</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspector o Profesor</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema debe registrar el atraso en pocos segundos desde que se lee la tarjeta, sin pasos adicionales.</t>
+          <t>El sistema debe registrar el atraso en pocos segundos desde que se lee la tarjeta, sin pasos adicionales.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.9</t>
+          <t>R.9</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protección de datos del alumno</t>
+          <t>Protección de datos del alumno</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Funcional</t>
+          <t>No Funcional</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema no debe usar datos biométricos ni guardar más información de la necesaria para identificar al alumno y su atraso.</t>
+          <t>El sistema no debe usar datos biométricos ni guardar más información de la necesaria para identificar al alumno y su atraso.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.10</t>
+          <t>R.10</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disponibilidad en el horario de entrada</t>
+          <t>Disponibilidad en el horario de entrada</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Funcional</t>
+          <t>No Funcional</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sistema debe estar funcionando y disponible durante todo el horario de ingreso de los estudiantes al liceo.</t>
+          <t>El sistema debe estar funcionando y disponible durante todo el horario de ingreso de los estudiantes al liceo.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+          <t>Solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>R.11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>R.12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>R.13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>R.14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>R.15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
